--- a/Configs/GameConfig/Datas/__enums__.xlsx
+++ b/Configs/GameConfig/Datas/__enums__.xlsx
@@ -1,20 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24045" windowHeight="12900"/>
+    <workbookView windowHeight="22180"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="158">
   <si>
     <t>##var</t>
   </si>
@@ -73,86 +86,451 @@
     <t>注释</t>
   </si>
   <si>
-    <t>item.EQuality</t>
+    <t>test.AccessFlag</t>
+  </si>
+  <si>
+    <t>WRITE</t>
+  </si>
+  <si>
+    <t>READ</t>
+  </si>
+  <si>
+    <t>TRUNCATE</t>
+  </si>
+  <si>
+    <t>NEW</t>
+  </si>
+  <si>
+    <t>READ_WRITE</t>
+  </si>
+  <si>
+    <t>WRITE|READ</t>
+  </si>
+  <si>
+    <t>位标记使用示例</t>
+  </si>
+  <si>
+    <t>stacklands.ECardCategory</t>
+  </si>
+  <si>
+    <t>STRUCTURE</t>
+  </si>
+  <si>
+    <t>VILLAGER</t>
+  </si>
+  <si>
+    <t>RESOURCE</t>
+  </si>
+  <si>
+    <t>IDEA</t>
+  </si>
+  <si>
+    <t>FOOD</t>
+  </si>
+  <si>
+    <t>MOB</t>
+  </si>
+  <si>
+    <t>LOCATION</t>
+  </si>
+  <si>
+    <t>RUMOR</t>
+  </si>
+  <si>
+    <t>EQUIPMENT</t>
+  </si>
+  <si>
+    <t>stacklands.ECardColor</t>
+  </si>
+  <si>
+    <t>PINK</t>
+  </si>
+  <si>
+    <t>BLACK</t>
+  </si>
+  <si>
+    <t>RED</t>
+  </si>
+  <si>
+    <t>GOLD</t>
+  </si>
+  <si>
+    <t>YELLOW</t>
+  </si>
+  <si>
+    <t>SILVER</t>
   </si>
   <si>
     <t>WHITE</t>
   </si>
   <si>
-    <t>白</t>
-  </si>
-  <si>
-    <t>最差品质</t>
+    <t>GREEN</t>
   </si>
   <si>
     <t>BLUE</t>
   </si>
   <si>
-    <t>蓝</t>
-  </si>
-  <si>
-    <t>蓝色的</t>
+    <t>ORANGE</t>
+  </si>
+  <si>
+    <t>LIGHT_ORANGE</t>
+  </si>
+  <si>
+    <t>BROWN</t>
   </si>
   <si>
     <t>PURPLE</t>
   </si>
   <si>
-    <t>紫</t>
-  </si>
-  <si>
-    <t>紫色的</t>
-  </si>
-  <si>
-    <t>RED</t>
-  </si>
-  <si>
-    <t>红</t>
-  </si>
-  <si>
-    <t>最高品质</t>
-  </si>
-  <si>
-    <t>test.AccessFlag</t>
-  </si>
-  <si>
-    <t>WRITE</t>
-  </si>
-  <si>
-    <t>READ</t>
-  </si>
-  <si>
-    <t>TRUNCATE</t>
-  </si>
-  <si>
-    <t>NEW</t>
-  </si>
-  <si>
-    <t>READ_WRITE</t>
-  </si>
-  <si>
-    <t>WRITE|READ</t>
-  </si>
-  <si>
-    <t>位标记使用示例</t>
+    <t>GRAY</t>
+  </si>
+  <si>
+    <t>stacklands.ECardTag</t>
+  </si>
+  <si>
+    <t>ADULT</t>
+  </si>
+  <si>
+    <t>WORKER</t>
+  </si>
+  <si>
+    <t>HUMAN</t>
+  </si>
+  <si>
+    <t>ANIMAL</t>
+  </si>
+  <si>
+    <t>HOSTILE</t>
+  </si>
+  <si>
+    <t>BOSS</t>
+  </si>
+  <si>
+    <t>BUILDING</t>
+  </si>
+  <si>
+    <t>RESOURCE_NODE</t>
+  </si>
+  <si>
+    <t>CURRENCY</t>
+  </si>
+  <si>
+    <t>FINITE</t>
+  </si>
+  <si>
+    <t>INFINITE</t>
+  </si>
+  <si>
+    <t>stacklands.EVerifyStatus</t>
+  </si>
+  <si>
+    <t>VERIFIED</t>
+  </si>
+  <si>
+    <t>PARTIAL</t>
+  </si>
+  <si>
+    <t>UNVERIFIED</t>
+  </si>
+  <si>
+    <t>CONFLICT</t>
+  </si>
+  <si>
+    <t>stacklands.EUnitFaction</t>
+  </si>
+  <si>
+    <t>FRIENDLY</t>
+  </si>
+  <si>
+    <t>stacklands.EAttackType</t>
+  </si>
+  <si>
+    <t>NONE</t>
+  </si>
+  <si>
+    <t>MELEE</t>
+  </si>
+  <si>
+    <t>RANGED</t>
+  </si>
+  <si>
+    <t>MAGIC</t>
+  </si>
+  <si>
+    <t>stacklands.EEquipmentSlot</t>
+  </si>
+  <si>
+    <t>HAND</t>
+  </si>
+  <si>
+    <t>BODY</t>
+  </si>
+  <si>
+    <t>HEAD</t>
+  </si>
+  <si>
+    <t>stacklands.EStructureType</t>
+  </si>
+  <si>
+    <t>HARVESTABLE</t>
+  </si>
+  <si>
+    <t>PRODUCTION</t>
+  </si>
+  <si>
+    <t>STORAGE</t>
+  </si>
+  <si>
+    <t>MARKET</t>
+  </si>
+  <si>
+    <t>HOUSING</t>
+  </si>
+  <si>
+    <t>PORTAL</t>
+  </si>
+  <si>
+    <t>SPECIAL</t>
+  </si>
+  <si>
+    <t>stacklands.ERecipeGroup</t>
+  </si>
+  <si>
+    <t>POPULATION</t>
+  </si>
+  <si>
+    <t>stacklands.ECardMatcher</t>
+  </si>
+  <si>
+    <t>EXACT</t>
+  </si>
+  <si>
+    <t>TAG</t>
+  </si>
+  <si>
+    <t>CATEGORY</t>
+  </si>
+  <si>
+    <t>stacklands.EConsumeMode</t>
+  </si>
+  <si>
+    <t>CONSUME</t>
+  </si>
+  <si>
+    <t>RETAIN</t>
+  </si>
+  <si>
+    <t>TRANSFORM</t>
+  </si>
+  <si>
+    <t>EQUIP</t>
+  </si>
+  <si>
+    <t>stacklands.EActionType</t>
+  </si>
+  <si>
+    <t>HARVEST</t>
+  </si>
+  <si>
+    <t>PRODUCE</t>
+  </si>
+  <si>
+    <t>EXPLORE</t>
+  </si>
+  <si>
+    <t>OPEN</t>
+  </si>
+  <si>
+    <t>SELL</t>
+  </si>
+  <si>
+    <t>BREED</t>
+  </si>
+  <si>
+    <t>GROW</t>
+  </si>
+  <si>
+    <t>SUMMON</t>
+  </si>
+  <si>
+    <t>TRADE</t>
+  </si>
+  <si>
+    <t>SPAWN</t>
+  </si>
+  <si>
+    <t>DEFEAT</t>
+  </si>
+  <si>
+    <t>stacklands.EWorkerRequirement</t>
+  </si>
+  <si>
+    <t>EXPLORER</t>
+  </si>
+  <si>
+    <t>stacklands.EOnceScope</t>
+  </si>
+  <si>
+    <t>RUN</t>
+  </si>
+  <si>
+    <t>PROFILE</t>
+  </si>
+  <si>
+    <t>stacklands.EConditionType</t>
+  </si>
+  <si>
+    <t>PEACEFUL_MODE</t>
+  </si>
+  <si>
+    <t>OWNED_COUNT_LESS_THAN</t>
+  </si>
+  <si>
+    <t>IDEA_UNDISCOVERED</t>
+  </si>
+  <si>
+    <t>ALL_IDEAS_DISCOVERED</t>
+  </si>
+  <si>
+    <t>PACK_PURCHASE_COUNT</t>
+  </si>
+  <si>
+    <t>MOON_AT_LEAST</t>
+  </si>
+  <si>
+    <t>stacklands.EPackAcquireMode</t>
+  </si>
+  <si>
+    <t>PURCHASE</t>
+  </si>
+  <si>
+    <t>AUTO_START</t>
+  </si>
+  <si>
+    <t>MILESTONE</t>
+  </si>
+  <si>
+    <t>stacklands.EQuestSeries</t>
+  </si>
+  <si>
+    <t>WELCOME</t>
+  </si>
+  <si>
+    <t>GRAND_SCHEME</t>
+  </si>
+  <si>
+    <t>POWER_SKILL</t>
+  </si>
+  <si>
+    <t>POTLUCK</t>
+  </si>
+  <si>
+    <t>DISCOVERY</t>
+  </si>
+  <si>
+    <t>WAYS_MEANS</t>
+  </si>
+  <si>
+    <t>CONSTRUCTION</t>
+  </si>
+  <si>
+    <t>LONGEVITY</t>
+  </si>
+  <si>
+    <t>stacklands.EConditionMode</t>
+  </si>
+  <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>ANY</t>
+  </si>
+  <si>
+    <t>stacklands.EQuestPersistence</t>
+  </si>
+  <si>
+    <t>stacklands.EQuestMetric</t>
+  </si>
+  <si>
+    <t>EVENT_COUNT</t>
+  </si>
+  <si>
+    <t>CARD_COUNT</t>
+  </si>
+  <si>
+    <t>TOTAL_FOOD</t>
+  </si>
+  <si>
+    <t>COIN_COUNT</t>
+  </si>
+  <si>
+    <t>IDEA_DISCOVERED_COUNT</t>
+  </si>
+  <si>
+    <t>REACH_MOON</t>
+  </si>
+  <si>
+    <t>PACK_UNLOCKED</t>
+  </si>
+  <si>
+    <t>PACK_OPENED</t>
+  </si>
+  <si>
+    <t>PACK_PURCHASED</t>
+  </si>
+  <si>
+    <t>CARD_OBTAINED</t>
+  </si>
+  <si>
+    <t>CARD_CREATED</t>
+  </si>
+  <si>
+    <t>CARD_KILLED</t>
+  </si>
+  <si>
+    <t>LOCATION_EXPLORED</t>
+  </si>
+  <si>
+    <t>STATE_CHECK</t>
+  </si>
+  <si>
+    <t>stacklands.ECompareOp</t>
+  </si>
+  <si>
+    <t>AT_LEAST</t>
+  </si>
+  <si>
+    <t>EQUAL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Carlito"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Carlito"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Carlito"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -306,7 +684,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -315,7 +693,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4CCCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,7 +896,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -516,17 +906,93 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FFA6A6A6"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="FFA6A6A6"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="FFA6A6A6"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FFA6A6A6"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFE7E6E6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE7E6E6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE7E6E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE7E6E6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE7E6E6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE7E6E6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE7E6E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE7E6E6"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFE7E6E6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE7E6E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFE7E6E6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE7E6E6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE7E6E6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE7E6E6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE7E6E6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE7E6E6"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFE7E6E6"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -628,32 +1094,23 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+  <cellStyleXfs count="50">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -662,43 +1119,46 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -710,139 +1170,371 @@
     <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
+  <cellStyles count="50">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="Normal" xfId="49"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -852,9 +1544,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ChatGPT">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="ChatGPT">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -862,160 +1554,100 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="ChatGPT">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="67000"/>
                 <a:lumMod val="110000"/>
                 <a:satMod val="105000"/>
-                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:tint val="73000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="103000"/>
-                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:tint val="81000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="109000"/>
-                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="94000"/>
+                <a:lumMod val="102000"/>
                 <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:shade val="100000"/>
+                <a:lumMod val="100000"/>
                 <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:shade val="78000"/>
                 <a:lumMod val="99000"/>
                 <a:satMod val="120000"/>
-                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -1023,26 +1655,23 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -1054,7 +1683,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -1072,22 +1701,22 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
@@ -1109,21 +1738,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <dimension ref="A1:L140"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="20.8761904761905" customWidth="1"/>
-    <col min="4" max="5" width="14.1238095238095" customWidth="1"/>
-    <col min="6" max="6" width="9.37142857142857" customWidth="1"/>
-    <col min="7" max="7" width="5" customWidth="1"/>
-    <col min="8" max="8" width="13.5047619047619" customWidth="1"/>
-    <col min="9" max="9" width="5.24761904761905" customWidth="1"/>
-    <col min="10" max="10" width="12.1238095238095" customWidth="1"/>
-    <col min="11" max="11" width="15.1238095238095" customWidth="1"/>
+    <col min="1" max="1" width="8.66911764705882" customWidth="1"/>
+    <col min="2" max="2" width="24.2205882352941" customWidth="1"/>
+    <col min="3" max="3" width="28.8897058823529" customWidth="1"/>
+    <col min="4" max="4" width="11.8897058823529" customWidth="1"/>
+    <col min="5" max="7" width="8.66911764705882" customWidth="1"/>
+    <col min="8" max="8" width="23.1102941176471" customWidth="1"/>
+    <col min="9" max="9" width="8.66911764705882" customWidth="1"/>
+    <col min="10" max="10" width="10.1102941176471" customWidth="1"/>
+    <col min="11" max="11" width="23.1102941176471" customWidth="1"/>
+    <col min="12" max="12" width="8.66911764705882" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" ht="18" customHeight="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1145,193 +1775,3093 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+    </row>
+    <row r="2" ht="18" customHeight="1" spans="1:12">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1" t="s">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="99" customHeight="1" spans="1:12">
-      <c r="A3" s="1" t="s">
+    <row r="3" ht="18" customHeight="1" spans="1:12">
+      <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1" t="s">
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="1"/>
-    </row>
-    <row r="4" spans="2:11">
-      <c r="B4" t="s">
+      <c r="L3" s="3"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="4"/>
+      <c r="B4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C4" t="b">
+      <c r="C4" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="D4" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5">
+        <v>1</v>
+      </c>
+      <c r="K4" s="5"/>
+      <c r="L4" s="6"/>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="4"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5">
+        <v>2</v>
+      </c>
+      <c r="K5" s="5"/>
+      <c r="L5" s="6"/>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="4"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5">
+        <v>4</v>
+      </c>
+      <c r="K6" s="5"/>
+      <c r="L6" s="6"/>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="4"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5">
+        <v>8</v>
+      </c>
+      <c r="K7" s="5"/>
+      <c r="L7" s="6"/>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="4"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L8" s="6"/>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" s="4"/>
+      <c r="B9" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="5">
         <v>0</v>
       </c>
-      <c r="D4" t="b">
+      <c r="D9" s="5">
         <v>1</v>
       </c>
-      <c r="H4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J4">
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5">
         <v>1</v>
       </c>
-      <c r="K4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="8:11">
-      <c r="H5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5">
+      <c r="K9" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L9" s="6"/>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" s="4"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5">
         <v>2</v>
       </c>
-      <c r="K5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="8:11">
-      <c r="H6" t="s">
-        <v>26</v>
-      </c>
-      <c r="I6" t="s">
-        <v>27</v>
-      </c>
-      <c r="J6">
+      <c r="K10" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="L10" s="6"/>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" s="4"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5">
         <v>3</v>
       </c>
-      <c r="K6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="8:11">
-      <c r="H7" t="s">
+      <c r="K11" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L11" s="6"/>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" s="4"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5">
+        <v>4</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="L12" s="6"/>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" s="4"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5">
+        <v>5</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="L13" s="6"/>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" s="4"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5">
+        <v>6</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="L14" s="6"/>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" s="4"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5">
+        <v>7</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L15" s="6"/>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" s="4"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5">
+        <v>8</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="L16" s="6"/>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" s="4"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5">
+        <v>9</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="L17" s="6"/>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" s="4"/>
+      <c r="B18" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="5">
+        <v>0</v>
+      </c>
+      <c r="D18" s="5">
+        <v>1</v>
+      </c>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5">
+        <v>1</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="L18" s="6"/>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" s="4"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5">
+        <v>2</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="L19" s="6"/>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" s="4"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5">
+        <v>3</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="L20" s="6"/>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" s="4"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5">
+        <v>4</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="L21" s="6"/>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" s="4"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5">
+        <v>5</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="L22" s="6"/>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" s="4"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5">
+        <v>6</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="L23" s="6"/>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" s="4"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5">
+        <v>7</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="L24" s="6"/>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" s="4"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5">
+        <v>8</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="L25" s="6"/>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26" s="4"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5">
+        <v>9</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="L26" s="6"/>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" s="4"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5">
+        <v>10</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="L27" s="6"/>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="A28" s="4"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5">
+        <v>11</v>
+      </c>
+      <c r="K28" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="L28" s="6"/>
+    </row>
+    <row r="29" spans="1:12">
+      <c r="A29" s="4"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="I29" s="5"/>
+      <c r="J29" s="5">
+        <v>12</v>
+      </c>
+      <c r="K29" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="L29" s="6"/>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="A30" s="4"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="I30" s="5"/>
+      <c r="J30" s="5">
+        <v>13</v>
+      </c>
+      <c r="K30" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L30" s="6"/>
+    </row>
+    <row r="31" spans="1:12">
+      <c r="A31" s="4"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="I31" s="5"/>
+      <c r="J31" s="5">
+        <v>14</v>
+      </c>
+      <c r="K31" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="L31" s="6"/>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="A32" s="4"/>
+      <c r="B32" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C32" s="5">
+        <v>0</v>
+      </c>
+      <c r="D32" s="5">
+        <v>1</v>
+      </c>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="I32" s="5"/>
+      <c r="J32" s="5">
+        <v>1</v>
+      </c>
+      <c r="K32" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="L32" s="6"/>
+    </row>
+    <row r="33" spans="1:12">
+      <c r="A33" s="4"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="I33" s="5"/>
+      <c r="J33" s="5">
+        <v>2</v>
+      </c>
+      <c r="K33" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L33" s="6"/>
+    </row>
+    <row r="34" spans="1:12">
+      <c r="A34" s="4"/>
+      <c r="B34" s="5"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="I34" s="5"/>
+      <c r="J34" s="5">
+        <v>3</v>
+      </c>
+      <c r="K34" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L34" s="6"/>
+    </row>
+    <row r="35" spans="1:12">
+      <c r="A35" s="4"/>
+      <c r="B35" s="5"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="I35" s="5"/>
+      <c r="J35" s="5">
+        <v>4</v>
+      </c>
+      <c r="K35" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="L35" s="6"/>
+    </row>
+    <row r="36" spans="1:12">
+      <c r="A36" s="4"/>
+      <c r="B36" s="5"/>
+      <c r="C36" s="5"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="I36" s="5"/>
+      <c r="J36" s="5">
+        <v>5</v>
+      </c>
+      <c r="K36" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="L36" s="6"/>
+    </row>
+    <row r="37" spans="1:12">
+      <c r="A37" s="4"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="I37" s="5"/>
+      <c r="J37" s="5">
+        <v>6</v>
+      </c>
+      <c r="K37" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="L37" s="6"/>
+    </row>
+    <row r="38" spans="1:12">
+      <c r="A38" s="4"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I38" s="5"/>
+      <c r="J38" s="5">
+        <v>7</v>
+      </c>
+      <c r="K38" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="L38" s="6"/>
+    </row>
+    <row r="39" spans="1:12">
+      <c r="A39" s="4"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="I39" s="5"/>
+      <c r="J39" s="5">
+        <v>8</v>
+      </c>
+      <c r="K39" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="L39" s="6"/>
+    </row>
+    <row r="40" spans="1:12">
+      <c r="A40" s="4"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I40" s="5"/>
+      <c r="J40" s="5">
+        <v>9</v>
+      </c>
+      <c r="K40" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="L40" s="6"/>
+    </row>
+    <row r="41" spans="1:12">
+      <c r="A41" s="4"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I41" s="5"/>
+      <c r="J41" s="5">
+        <v>10</v>
+      </c>
+      <c r="K41" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="L41" s="6"/>
+    </row>
+    <row r="42" spans="1:12">
+      <c r="A42" s="4"/>
+      <c r="B42" s="5"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="5"/>
+      <c r="H42" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I42" s="5"/>
+      <c r="J42" s="5">
+        <v>11</v>
+      </c>
+      <c r="K42" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="L42" s="6"/>
+    </row>
+    <row r="43" spans="1:12">
+      <c r="A43" s="4"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="5"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="I43" s="5"/>
+      <c r="J43" s="5">
+        <v>12</v>
+      </c>
+      <c r="K43" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="L43" s="6"/>
+    </row>
+    <row r="44" spans="1:12">
+      <c r="A44" s="4"/>
+      <c r="B44" s="5"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I44" s="5"/>
+      <c r="J44" s="5">
+        <v>13</v>
+      </c>
+      <c r="K44" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L44" s="6"/>
+    </row>
+    <row r="45" spans="1:12">
+      <c r="A45" s="4"/>
+      <c r="B45" s="5"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="I45" s="5"/>
+      <c r="J45" s="5">
+        <v>14</v>
+      </c>
+      <c r="K45" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="L45" s="6"/>
+    </row>
+    <row r="46" spans="1:12">
+      <c r="A46" s="4"/>
+      <c r="B46" s="5"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="5"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="I46" s="5"/>
+      <c r="J46" s="5">
+        <v>15</v>
+      </c>
+      <c r="K46" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="L46" s="6"/>
+    </row>
+    <row r="47" spans="1:12">
+      <c r="A47" s="4"/>
+      <c r="B47" s="5"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="5"/>
+      <c r="F47" s="5"/>
+      <c r="G47" s="5"/>
+      <c r="H47" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="I47" s="5"/>
+      <c r="J47" s="5">
+        <v>16</v>
+      </c>
+      <c r="K47" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="L47" s="6"/>
+    </row>
+    <row r="48" spans="1:12">
+      <c r="A48" s="4"/>
+      <c r="B48" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C48" s="5">
+        <v>0</v>
+      </c>
+      <c r="D48" s="5">
+        <v>1</v>
+      </c>
+      <c r="E48" s="5"/>
+      <c r="F48" s="5"/>
+      <c r="G48" s="5"/>
+      <c r="H48" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I48" s="5"/>
+      <c r="J48" s="5">
+        <v>1</v>
+      </c>
+      <c r="K48" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="L48" s="6"/>
+    </row>
+    <row r="49" spans="1:12">
+      <c r="A49" s="4"/>
+      <c r="B49" s="5"/>
+      <c r="C49" s="5"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="5"/>
+      <c r="F49" s="5"/>
+      <c r="G49" s="5"/>
+      <c r="H49" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="I49" s="5"/>
+      <c r="J49" s="5">
+        <v>2</v>
+      </c>
+      <c r="K49" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="L49" s="6"/>
+    </row>
+    <row r="50" spans="1:12">
+      <c r="A50" s="4"/>
+      <c r="B50" s="5"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="5"/>
+      <c r="F50" s="5"/>
+      <c r="G50" s="5"/>
+      <c r="H50" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="I50" s="5"/>
+      <c r="J50" s="5">
+        <v>3</v>
+      </c>
+      <c r="K50" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="L50" s="6"/>
+    </row>
+    <row r="51" spans="1:12">
+      <c r="A51" s="4"/>
+      <c r="B51" s="5"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="5"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="5"/>
+      <c r="G51" s="5"/>
+      <c r="H51" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="I51" s="5"/>
+      <c r="J51" s="5">
+        <v>4</v>
+      </c>
+      <c r="K51" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="L51" s="6"/>
+    </row>
+    <row r="52" spans="1:12">
+      <c r="A52" s="4"/>
+      <c r="B52" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C52" s="5">
+        <v>0</v>
+      </c>
+      <c r="D52" s="5">
+        <v>1</v>
+      </c>
+      <c r="E52" s="5"/>
+      <c r="F52" s="5"/>
+      <c r="G52" s="5"/>
+      <c r="H52" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="I52" s="5"/>
+      <c r="J52" s="5">
+        <v>1</v>
+      </c>
+      <c r="K52" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="L52" s="6"/>
+    </row>
+    <row r="53" spans="1:12">
+      <c r="A53" s="4"/>
+      <c r="B53" s="5"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="5"/>
+      <c r="E53" s="5"/>
+      <c r="F53" s="5"/>
+      <c r="G53" s="5"/>
+      <c r="H53" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="I53" s="5"/>
+      <c r="J53" s="5">
+        <v>2</v>
+      </c>
+      <c r="K53" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="L53" s="6"/>
+    </row>
+    <row r="54" spans="1:12">
+      <c r="A54" s="4"/>
+      <c r="B54" s="5"/>
+      <c r="C54" s="5"/>
+      <c r="D54" s="5"/>
+      <c r="E54" s="5"/>
+      <c r="F54" s="5"/>
+      <c r="G54" s="5"/>
+      <c r="H54" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="I54" s="5"/>
+      <c r="J54" s="5">
+        <v>3</v>
+      </c>
+      <c r="K54" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="L54" s="6"/>
+    </row>
+    <row r="55" spans="1:12">
+      <c r="A55" s="4"/>
+      <c r="B55" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C55" s="5">
+        <v>0</v>
+      </c>
+      <c r="D55" s="5">
+        <v>1</v>
+      </c>
+      <c r="E55" s="5"/>
+      <c r="F55" s="5"/>
+      <c r="G55" s="5"/>
+      <c r="H55" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="I55" s="5"/>
+      <c r="J55" s="5">
+        <v>1</v>
+      </c>
+      <c r="K55" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="L55" s="6"/>
+    </row>
+    <row r="56" spans="1:12">
+      <c r="A56" s="4"/>
+      <c r="B56" s="5"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="5"/>
+      <c r="E56" s="5"/>
+      <c r="F56" s="5"/>
+      <c r="G56" s="5"/>
+      <c r="H56" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="I56" s="5"/>
+      <c r="J56" s="5">
+        <v>2</v>
+      </c>
+      <c r="K56" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="L56" s="6"/>
+    </row>
+    <row r="57" spans="1:12">
+      <c r="A57" s="4"/>
+      <c r="B57" s="5"/>
+      <c r="C57" s="5"/>
+      <c r="D57" s="5"/>
+      <c r="E57" s="5"/>
+      <c r="F57" s="5"/>
+      <c r="G57" s="5"/>
+      <c r="H57" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I57" s="5"/>
+      <c r="J57" s="5">
+        <v>3</v>
+      </c>
+      <c r="K57" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="L57" s="6"/>
+    </row>
+    <row r="58" spans="1:12">
+      <c r="A58" s="4"/>
+      <c r="B58" s="5"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="5"/>
+      <c r="E58" s="5"/>
+      <c r="F58" s="5"/>
+      <c r="G58" s="5"/>
+      <c r="H58" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I58" s="5"/>
+      <c r="J58" s="5">
+        <v>4</v>
+      </c>
+      <c r="K58" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L58" s="6"/>
+    </row>
+    <row r="59" spans="1:12">
+      <c r="A59" s="4"/>
+      <c r="B59" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C59" s="5">
+        <v>0</v>
+      </c>
+      <c r="D59" s="5">
+        <v>1</v>
+      </c>
+      <c r="E59" s="5"/>
+      <c r="F59" s="5"/>
+      <c r="G59" s="5"/>
+      <c r="H59" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="I59" s="5"/>
+      <c r="J59" s="5">
+        <v>1</v>
+      </c>
+      <c r="K59" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="L59" s="6"/>
+    </row>
+    <row r="60" spans="1:12">
+      <c r="A60" s="4"/>
+      <c r="B60" s="5"/>
+      <c r="C60" s="5"/>
+      <c r="D60" s="5"/>
+      <c r="E60" s="5"/>
+      <c r="F60" s="5"/>
+      <c r="G60" s="5"/>
+      <c r="H60" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="I60" s="5"/>
+      <c r="J60" s="5">
+        <v>2</v>
+      </c>
+      <c r="K60" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="L60" s="6"/>
+    </row>
+    <row r="61" spans="1:12">
+      <c r="A61" s="4"/>
+      <c r="B61" s="5"/>
+      <c r="C61" s="5"/>
+      <c r="D61" s="5"/>
+      <c r="E61" s="5"/>
+      <c r="F61" s="5"/>
+      <c r="G61" s="5"/>
+      <c r="H61" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="I61" s="5"/>
+      <c r="J61" s="5">
+        <v>3</v>
+      </c>
+      <c r="K61" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="L61" s="6"/>
+    </row>
+    <row r="62" spans="1:12">
+      <c r="A62" s="4"/>
+      <c r="B62" s="5"/>
+      <c r="C62" s="5"/>
+      <c r="D62" s="5"/>
+      <c r="E62" s="5"/>
+      <c r="F62" s="5"/>
+      <c r="G62" s="5"/>
+      <c r="H62" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="I62" s="5"/>
+      <c r="J62" s="5">
+        <v>4</v>
+      </c>
+      <c r="K62" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="L62" s="6"/>
+    </row>
+    <row r="63" spans="1:12">
+      <c r="A63" s="4"/>
+      <c r="B63" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C63" s="5">
+        <v>0</v>
+      </c>
+      <c r="D63" s="5">
+        <v>1</v>
+      </c>
+      <c r="E63" s="5"/>
+      <c r="F63" s="5"/>
+      <c r="G63" s="5"/>
+      <c r="H63" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="I63" s="5"/>
+      <c r="J63" s="5">
+        <v>1</v>
+      </c>
+      <c r="K63" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="L63" s="6"/>
+    </row>
+    <row r="64" spans="1:12">
+      <c r="A64" s="4"/>
+      <c r="B64" s="5"/>
+      <c r="C64" s="5"/>
+      <c r="D64" s="5"/>
+      <c r="E64" s="5"/>
+      <c r="F64" s="5"/>
+      <c r="G64" s="5"/>
+      <c r="H64" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="I64" s="5"/>
+      <c r="J64" s="5">
+        <v>2</v>
+      </c>
+      <c r="K64" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="L64" s="6"/>
+    </row>
+    <row r="65" spans="1:12">
+      <c r="A65" s="4"/>
+      <c r="B65" s="5"/>
+      <c r="C65" s="5"/>
+      <c r="D65" s="5"/>
+      <c r="E65" s="5"/>
+      <c r="F65" s="5"/>
+      <c r="G65" s="5"/>
+      <c r="H65" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="I65" s="5"/>
+      <c r="J65" s="5">
+        <v>3</v>
+      </c>
+      <c r="K65" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="L65" s="6"/>
+    </row>
+    <row r="66" spans="1:12">
+      <c r="A66" s="4"/>
+      <c r="B66" s="5"/>
+      <c r="C66" s="5"/>
+      <c r="D66" s="5"/>
+      <c r="E66" s="5"/>
+      <c r="F66" s="5"/>
+      <c r="G66" s="5"/>
+      <c r="H66" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="I66" s="5"/>
+      <c r="J66" s="5">
+        <v>4</v>
+      </c>
+      <c r="K66" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="L66" s="6"/>
+    </row>
+    <row r="67" spans="1:12">
+      <c r="A67" s="4"/>
+      <c r="B67" s="5"/>
+      <c r="C67" s="5"/>
+      <c r="D67" s="5"/>
+      <c r="E67" s="5"/>
+      <c r="F67" s="5"/>
+      <c r="G67" s="5"/>
+      <c r="H67" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="I67" s="5"/>
+      <c r="J67" s="5">
+        <v>5</v>
+      </c>
+      <c r="K67" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="L67" s="6"/>
+    </row>
+    <row r="68" spans="1:12">
+      <c r="A68" s="4"/>
+      <c r="B68" s="5"/>
+      <c r="C68" s="5"/>
+      <c r="D68" s="5"/>
+      <c r="E68" s="5"/>
+      <c r="F68" s="5"/>
+      <c r="G68" s="5"/>
+      <c r="H68" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="I68" s="5"/>
+      <c r="J68" s="5">
+        <v>6</v>
+      </c>
+      <c r="K68" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="L68" s="6"/>
+    </row>
+    <row r="69" spans="1:12">
+      <c r="A69" s="4"/>
+      <c r="B69" s="5"/>
+      <c r="C69" s="5"/>
+      <c r="D69" s="5"/>
+      <c r="E69" s="5"/>
+      <c r="F69" s="5"/>
+      <c r="G69" s="5"/>
+      <c r="H69" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="I69" s="5"/>
+      <c r="J69" s="5">
+        <v>7</v>
+      </c>
+      <c r="K69" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="L69" s="6"/>
+    </row>
+    <row r="70" spans="1:12">
+      <c r="A70" s="4"/>
+      <c r="B70" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C70" s="5">
+        <v>0</v>
+      </c>
+      <c r="D70" s="5">
+        <v>1</v>
+      </c>
+      <c r="E70" s="5"/>
+      <c r="F70" s="5"/>
+      <c r="G70" s="5"/>
+      <c r="H70" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I70" s="5"/>
+      <c r="J70" s="5">
+        <v>1</v>
+      </c>
+      <c r="K70" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="L70" s="6"/>
+    </row>
+    <row r="71" spans="1:12">
+      <c r="A71" s="4"/>
+      <c r="B71" s="5"/>
+      <c r="C71" s="5"/>
+      <c r="D71" s="5"/>
+      <c r="E71" s="5"/>
+      <c r="F71" s="5"/>
+      <c r="G71" s="5"/>
+      <c r="H71" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I71" s="5"/>
+      <c r="J71" s="5">
+        <v>2</v>
+      </c>
+      <c r="K71" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L71" s="6"/>
+    </row>
+    <row r="72" spans="1:12">
+      <c r="A72" s="4"/>
+      <c r="B72" s="5"/>
+      <c r="C72" s="5"/>
+      <c r="D72" s="5"/>
+      <c r="E72" s="5"/>
+      <c r="F72" s="5"/>
+      <c r="G72" s="5"/>
+      <c r="H72" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I72" s="5"/>
+      <c r="J72" s="5">
+        <v>3</v>
+      </c>
+      <c r="K72" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="L72" s="6"/>
+    </row>
+    <row r="73" spans="1:12">
+      <c r="A73" s="4"/>
+      <c r="B73" s="5"/>
+      <c r="C73" s="5"/>
+      <c r="D73" s="5"/>
+      <c r="E73" s="5"/>
+      <c r="F73" s="5"/>
+      <c r="G73" s="5"/>
+      <c r="H73" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="I73" s="5"/>
+      <c r="J73" s="5">
+        <v>4</v>
+      </c>
+      <c r="K73" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="L73" s="6"/>
+    </row>
+    <row r="74" spans="1:12">
+      <c r="A74" s="4"/>
+      <c r="B74" s="5"/>
+      <c r="C74" s="5"/>
+      <c r="D74" s="5"/>
+      <c r="E74" s="5"/>
+      <c r="F74" s="5"/>
+      <c r="G74" s="5"/>
+      <c r="H74" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="I74" s="5"/>
+      <c r="J74" s="5">
+        <v>5</v>
+      </c>
+      <c r="K74" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="L74" s="6"/>
+    </row>
+    <row r="75" spans="1:12">
+      <c r="A75" s="4"/>
+      <c r="B75" s="5"/>
+      <c r="C75" s="5"/>
+      <c r="D75" s="5"/>
+      <c r="E75" s="5"/>
+      <c r="F75" s="5"/>
+      <c r="G75" s="5"/>
+      <c r="H75" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="I75" s="5"/>
+      <c r="J75" s="5">
+        <v>6</v>
+      </c>
+      <c r="K75" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="L75" s="6"/>
+    </row>
+    <row r="76" spans="1:12">
+      <c r="A76" s="4"/>
+      <c r="B76" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C76" s="5">
+        <v>0</v>
+      </c>
+      <c r="D76" s="5">
+        <v>1</v>
+      </c>
+      <c r="E76" s="5"/>
+      <c r="F76" s="5"/>
+      <c r="G76" s="5"/>
+      <c r="H76" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="I76" s="5"/>
+      <c r="J76" s="5">
+        <v>1</v>
+      </c>
+      <c r="K76" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="L76" s="6"/>
+    </row>
+    <row r="77" spans="1:12">
+      <c r="A77" s="4"/>
+      <c r="B77" s="5"/>
+      <c r="C77" s="5"/>
+      <c r="D77" s="5"/>
+      <c r="E77" s="5"/>
+      <c r="F77" s="5"/>
+      <c r="G77" s="5"/>
+      <c r="H77" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="I77" s="5"/>
+      <c r="J77" s="5">
+        <v>2</v>
+      </c>
+      <c r="K77" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="L77" s="6"/>
+    </row>
+    <row r="78" spans="1:12">
+      <c r="A78" s="4"/>
+      <c r="B78" s="5"/>
+      <c r="C78" s="5"/>
+      <c r="D78" s="5"/>
+      <c r="E78" s="5"/>
+      <c r="F78" s="5"/>
+      <c r="G78" s="5"/>
+      <c r="H78" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="I78" s="5"/>
+      <c r="J78" s="5">
+        <v>3</v>
+      </c>
+      <c r="K78" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="L78" s="6"/>
+    </row>
+    <row r="79" spans="1:12">
+      <c r="A79" s="4"/>
+      <c r="B79" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C79" s="5">
+        <v>0</v>
+      </c>
+      <c r="D79" s="5">
+        <v>1</v>
+      </c>
+      <c r="E79" s="5"/>
+      <c r="F79" s="5"/>
+      <c r="G79" s="5"/>
+      <c r="H79" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="I79" s="5"/>
+      <c r="J79" s="5">
+        <v>1</v>
+      </c>
+      <c r="K79" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="L79" s="6"/>
+    </row>
+    <row r="80" spans="1:12">
+      <c r="A80" s="4"/>
+      <c r="B80" s="5"/>
+      <c r="C80" s="5"/>
+      <c r="D80" s="5"/>
+      <c r="E80" s="5"/>
+      <c r="F80" s="5"/>
+      <c r="G80" s="5"/>
+      <c r="H80" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="I80" s="5"/>
+      <c r="J80" s="5">
+        <v>2</v>
+      </c>
+      <c r="K80" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="L80" s="6"/>
+    </row>
+    <row r="81" spans="1:12">
+      <c r="A81" s="4"/>
+      <c r="B81" s="5"/>
+      <c r="C81" s="5"/>
+      <c r="D81" s="5"/>
+      <c r="E81" s="5"/>
+      <c r="F81" s="5"/>
+      <c r="G81" s="5"/>
+      <c r="H81" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="I81" s="5"/>
+      <c r="J81" s="5">
+        <v>3</v>
+      </c>
+      <c r="K81" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="L81" s="6"/>
+    </row>
+    <row r="82" spans="1:12">
+      <c r="A82" s="4"/>
+      <c r="B82" s="5"/>
+      <c r="C82" s="5"/>
+      <c r="D82" s="5"/>
+      <c r="E82" s="5"/>
+      <c r="F82" s="5"/>
+      <c r="G82" s="5"/>
+      <c r="H82" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="I82" s="5"/>
+      <c r="J82" s="5">
+        <v>4</v>
+      </c>
+      <c r="K82" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="L82" s="6"/>
+    </row>
+    <row r="83" spans="1:12">
+      <c r="A83" s="4"/>
+      <c r="B83" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C83" s="5">
+        <v>0</v>
+      </c>
+      <c r="D83" s="5">
+        <v>1</v>
+      </c>
+      <c r="E83" s="5"/>
+      <c r="F83" s="5"/>
+      <c r="G83" s="5"/>
+      <c r="H83" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="I83" s="5"/>
+      <c r="J83" s="5">
+        <v>1</v>
+      </c>
+      <c r="K83" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="L83" s="6"/>
+    </row>
+    <row r="84" spans="1:12">
+      <c r="A84" s="4"/>
+      <c r="B84" s="5"/>
+      <c r="C84" s="5"/>
+      <c r="D84" s="5"/>
+      <c r="E84" s="5"/>
+      <c r="F84" s="5"/>
+      <c r="G84" s="5"/>
+      <c r="H84" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="I84" s="5"/>
+      <c r="J84" s="5">
+        <v>2</v>
+      </c>
+      <c r="K84" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="L84" s="6"/>
+    </row>
+    <row r="85" spans="1:12">
+      <c r="A85" s="4"/>
+      <c r="B85" s="5"/>
+      <c r="C85" s="5"/>
+      <c r="D85" s="5"/>
+      <c r="E85" s="5"/>
+      <c r="F85" s="5"/>
+      <c r="G85" s="5"/>
+      <c r="H85" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="I85" s="5"/>
+      <c r="J85" s="5">
+        <v>3</v>
+      </c>
+      <c r="K85" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="L85" s="6"/>
+    </row>
+    <row r="86" spans="1:12">
+      <c r="A86" s="4"/>
+      <c r="B86" s="5"/>
+      <c r="C86" s="5"/>
+      <c r="D86" s="5"/>
+      <c r="E86" s="5"/>
+      <c r="F86" s="5"/>
+      <c r="G86" s="5"/>
+      <c r="H86" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="I86" s="5"/>
+      <c r="J86" s="5">
+        <v>4</v>
+      </c>
+      <c r="K86" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="L86" s="6"/>
+    </row>
+    <row r="87" spans="1:12">
+      <c r="A87" s="4"/>
+      <c r="B87" s="5"/>
+      <c r="C87" s="5"/>
+      <c r="D87" s="5"/>
+      <c r="E87" s="5"/>
+      <c r="F87" s="5"/>
+      <c r="G87" s="5"/>
+      <c r="H87" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I87" s="5"/>
+      <c r="J87" s="5">
+        <v>5</v>
+      </c>
+      <c r="K87" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="L87" s="6"/>
+    </row>
+    <row r="88" spans="1:12">
+      <c r="A88" s="4"/>
+      <c r="B88" s="5"/>
+      <c r="C88" s="5"/>
+      <c r="D88" s="5"/>
+      <c r="E88" s="5"/>
+      <c r="F88" s="5"/>
+      <c r="G88" s="5"/>
+      <c r="H88" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="I88" s="5"/>
+      <c r="J88" s="5">
+        <v>6</v>
+      </c>
+      <c r="K88" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="L88" s="6"/>
+    </row>
+    <row r="89" spans="1:12">
+      <c r="A89" s="4"/>
+      <c r="B89" s="5"/>
+      <c r="C89" s="5"/>
+      <c r="D89" s="5"/>
+      <c r="E89" s="5"/>
+      <c r="F89" s="5"/>
+      <c r="G89" s="5"/>
+      <c r="H89" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="I89" s="5"/>
+      <c r="J89" s="5">
+        <v>7</v>
+      </c>
+      <c r="K89" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="L89" s="6"/>
+    </row>
+    <row r="90" spans="1:12">
+      <c r="A90" s="4"/>
+      <c r="B90" s="5"/>
+      <c r="C90" s="5"/>
+      <c r="D90" s="5"/>
+      <c r="E90" s="5"/>
+      <c r="F90" s="5"/>
+      <c r="G90" s="5"/>
+      <c r="H90" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="I90" s="5"/>
+      <c r="J90" s="5">
+        <v>8</v>
+      </c>
+      <c r="K90" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="L90" s="6"/>
+    </row>
+    <row r="91" spans="1:12">
+      <c r="A91" s="4"/>
+      <c r="B91" s="5"/>
+      <c r="C91" s="5"/>
+      <c r="D91" s="5"/>
+      <c r="E91" s="5"/>
+      <c r="F91" s="5"/>
+      <c r="G91" s="5"/>
+      <c r="H91" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="I91" s="5"/>
+      <c r="J91" s="5">
+        <v>9</v>
+      </c>
+      <c r="K91" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="L91" s="6"/>
+    </row>
+    <row r="92" spans="1:12">
+      <c r="A92" s="4"/>
+      <c r="B92" s="5"/>
+      <c r="C92" s="5"/>
+      <c r="D92" s="5"/>
+      <c r="E92" s="5"/>
+      <c r="F92" s="5"/>
+      <c r="G92" s="5"/>
+      <c r="H92" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="I92" s="5"/>
+      <c r="J92" s="5">
+        <v>10</v>
+      </c>
+      <c r="K92" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="L92" s="6"/>
+    </row>
+    <row r="93" spans="1:12">
+      <c r="A93" s="4"/>
+      <c r="B93" s="5"/>
+      <c r="C93" s="5"/>
+      <c r="D93" s="5"/>
+      <c r="E93" s="5"/>
+      <c r="F93" s="5"/>
+      <c r="G93" s="5"/>
+      <c r="H93" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="I93" s="5"/>
+      <c r="J93" s="5">
+        <v>11</v>
+      </c>
+      <c r="K93" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="L93" s="6"/>
+    </row>
+    <row r="94" spans="1:12">
+      <c r="A94" s="4"/>
+      <c r="B94" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C94" s="5">
+        <v>0</v>
+      </c>
+      <c r="D94" s="5">
+        <v>1</v>
+      </c>
+      <c r="E94" s="5"/>
+      <c r="F94" s="5"/>
+      <c r="G94" s="5"/>
+      <c r="H94" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="I94" s="5"/>
+      <c r="J94" s="5">
+        <v>1</v>
+      </c>
+      <c r="K94" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="L94" s="6"/>
+    </row>
+    <row r="95" spans="1:12">
+      <c r="A95" s="4"/>
+      <c r="B95" s="5"/>
+      <c r="C95" s="5"/>
+      <c r="D95" s="5"/>
+      <c r="E95" s="5"/>
+      <c r="F95" s="5"/>
+      <c r="G95" s="5"/>
+      <c r="H95" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="I95" s="5"/>
+      <c r="J95" s="5">
+        <v>2</v>
+      </c>
+      <c r="K95" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L95" s="6"/>
+    </row>
+    <row r="96" spans="1:12">
+      <c r="A96" s="4"/>
+      <c r="B96" s="5"/>
+      <c r="C96" s="5"/>
+      <c r="D96" s="5"/>
+      <c r="E96" s="5"/>
+      <c r="F96" s="5"/>
+      <c r="G96" s="5"/>
+      <c r="H96" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="I96" s="5"/>
+      <c r="J96" s="5">
+        <v>3</v>
+      </c>
+      <c r="K96" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="L96" s="6"/>
+    </row>
+    <row r="97" spans="1:12">
+      <c r="A97" s="4"/>
+      <c r="B97" s="5"/>
+      <c r="C97" s="5"/>
+      <c r="D97" s="5"/>
+      <c r="E97" s="5"/>
+      <c r="F97" s="5"/>
+      <c r="G97" s="5"/>
+      <c r="H97" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="I97" s="5"/>
+      <c r="J97" s="5">
+        <v>4</v>
+      </c>
+      <c r="K97" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L97" s="6"/>
+    </row>
+    <row r="98" spans="1:12">
+      <c r="A98" s="4"/>
+      <c r="B98" s="5"/>
+      <c r="C98" s="5"/>
+      <c r="D98" s="5"/>
+      <c r="E98" s="5"/>
+      <c r="F98" s="5"/>
+      <c r="G98" s="5"/>
+      <c r="H98" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="I7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J7">
+      <c r="I98" s="5"/>
+      <c r="J98" s="5">
+        <v>5</v>
+      </c>
+      <c r="K98" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="L98" s="6"/>
+    </row>
+    <row r="99" spans="1:12">
+      <c r="A99" s="4"/>
+      <c r="B99" s="5"/>
+      <c r="C99" s="5"/>
+      <c r="D99" s="5"/>
+      <c r="E99" s="5"/>
+      <c r="F99" s="5"/>
+      <c r="G99" s="5"/>
+      <c r="H99" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="I99" s="5"/>
+      <c r="J99" s="5">
+        <v>6</v>
+      </c>
+      <c r="K99" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="L99" s="6"/>
+    </row>
+    <row r="100" spans="1:12">
+      <c r="A100" s="4"/>
+      <c r="B100" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="C100" s="5">
+        <v>0</v>
+      </c>
+      <c r="D100" s="5">
+        <v>1</v>
+      </c>
+      <c r="E100" s="5"/>
+      <c r="F100" s="5"/>
+      <c r="G100" s="5"/>
+      <c r="H100" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="I100" s="5"/>
+      <c r="J100" s="5">
+        <v>1</v>
+      </c>
+      <c r="K100" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="L100" s="6"/>
+    </row>
+    <row r="101" spans="1:12">
+      <c r="A101" s="4"/>
+      <c r="B101" s="5"/>
+      <c r="C101" s="5"/>
+      <c r="D101" s="5"/>
+      <c r="E101" s="5"/>
+      <c r="F101" s="5"/>
+      <c r="G101" s="5"/>
+      <c r="H101" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="I101" s="5"/>
+      <c r="J101" s="5">
+        <v>2</v>
+      </c>
+      <c r="K101" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="L101" s="6"/>
+    </row>
+    <row r="102" spans="1:12">
+      <c r="A102" s="4"/>
+      <c r="B102" s="5"/>
+      <c r="C102" s="5"/>
+      <c r="D102" s="5"/>
+      <c r="E102" s="5"/>
+      <c r="F102" s="5"/>
+      <c r="G102" s="5"/>
+      <c r="H102" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="I102" s="5"/>
+      <c r="J102" s="5">
+        <v>3</v>
+      </c>
+      <c r="K102" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="L102" s="6"/>
+    </row>
+    <row r="103" spans="1:12">
+      <c r="A103" s="4"/>
+      <c r="B103" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C103" s="5">
+        <v>0</v>
+      </c>
+      <c r="D103" s="5">
+        <v>1</v>
+      </c>
+      <c r="E103" s="5"/>
+      <c r="F103" s="5"/>
+      <c r="G103" s="5"/>
+      <c r="H103" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="I103" s="5"/>
+      <c r="J103" s="5">
+        <v>1</v>
+      </c>
+      <c r="K103" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="L103" s="6"/>
+    </row>
+    <row r="104" spans="1:12">
+      <c r="A104" s="4"/>
+      <c r="B104" s="5"/>
+      <c r="C104" s="5"/>
+      <c r="D104" s="5"/>
+      <c r="E104" s="5"/>
+      <c r="F104" s="5"/>
+      <c r="G104" s="5"/>
+      <c r="H104" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="I104" s="5"/>
+      <c r="J104" s="5">
+        <v>2</v>
+      </c>
+      <c r="K104" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="L104" s="6"/>
+    </row>
+    <row r="105" spans="1:12">
+      <c r="A105" s="4"/>
+      <c r="B105" s="5"/>
+      <c r="C105" s="5"/>
+      <c r="D105" s="5"/>
+      <c r="E105" s="5"/>
+      <c r="F105" s="5"/>
+      <c r="G105" s="5"/>
+      <c r="H105" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="I105" s="5"/>
+      <c r="J105" s="5">
+        <v>3</v>
+      </c>
+      <c r="K105" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="L105" s="6"/>
+    </row>
+    <row r="106" spans="1:12">
+      <c r="A106" s="4"/>
+      <c r="B106" s="5"/>
+      <c r="C106" s="5"/>
+      <c r="D106" s="5"/>
+      <c r="E106" s="5"/>
+      <c r="F106" s="5"/>
+      <c r="G106" s="5"/>
+      <c r="H106" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="I106" s="5"/>
+      <c r="J106" s="5">
         <v>4</v>
       </c>
-      <c r="K7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10">
-      <c r="B8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" t="b">
+      <c r="K106" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="L106" s="6"/>
+    </row>
+    <row r="107" spans="1:12">
+      <c r="A107" s="4"/>
+      <c r="B107" s="5"/>
+      <c r="C107" s="5"/>
+      <c r="D107" s="5"/>
+      <c r="E107" s="5"/>
+      <c r="F107" s="5"/>
+      <c r="G107" s="5"/>
+      <c r="H107" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="I107" s="5"/>
+      <c r="J107" s="5">
+        <v>5</v>
+      </c>
+      <c r="K107" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="L107" s="6"/>
+    </row>
+    <row r="108" spans="1:12">
+      <c r="A108" s="4"/>
+      <c r="B108" s="5"/>
+      <c r="C108" s="5"/>
+      <c r="D108" s="5"/>
+      <c r="E108" s="5"/>
+      <c r="F108" s="5"/>
+      <c r="G108" s="5"/>
+      <c r="H108" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="I108" s="5"/>
+      <c r="J108" s="5">
+        <v>6</v>
+      </c>
+      <c r="K108" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="L108" s="6"/>
+    </row>
+    <row r="109" spans="1:12">
+      <c r="A109" s="4"/>
+      <c r="B109" s="5"/>
+      <c r="C109" s="5"/>
+      <c r="D109" s="5"/>
+      <c r="E109" s="5"/>
+      <c r="F109" s="5"/>
+      <c r="G109" s="5"/>
+      <c r="H109" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="I109" s="5"/>
+      <c r="J109" s="5">
+        <v>7</v>
+      </c>
+      <c r="K109" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="L109" s="6"/>
+    </row>
+    <row r="110" spans="1:12">
+      <c r="A110" s="4"/>
+      <c r="B110" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C110" s="5">
+        <v>0</v>
+      </c>
+      <c r="D110" s="5">
         <v>1</v>
       </c>
-      <c r="D8" t="b">
+      <c r="E110" s="5"/>
+      <c r="F110" s="5"/>
+      <c r="G110" s="5"/>
+      <c r="H110" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="I110" s="5"/>
+      <c r="J110" s="5">
         <v>1</v>
       </c>
-      <c r="H8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J8">
+      <c r="K110" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="L110" s="6"/>
+    </row>
+    <row r="111" spans="1:12">
+      <c r="A111" s="4"/>
+      <c r="B111" s="5"/>
+      <c r="C111" s="5"/>
+      <c r="D111" s="5"/>
+      <c r="E111" s="5"/>
+      <c r="F111" s="5"/>
+      <c r="G111" s="5"/>
+      <c r="H111" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="I111" s="5"/>
+      <c r="J111" s="5">
+        <v>2</v>
+      </c>
+      <c r="K111" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="L111" s="6"/>
+    </row>
+    <row r="112" spans="1:12">
+      <c r="A112" s="4"/>
+      <c r="B112" s="5"/>
+      <c r="C112" s="5"/>
+      <c r="D112" s="5"/>
+      <c r="E112" s="5"/>
+      <c r="F112" s="5"/>
+      <c r="G112" s="5"/>
+      <c r="H112" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="I112" s="5"/>
+      <c r="J112" s="5">
+        <v>3</v>
+      </c>
+      <c r="K112" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="L112" s="6"/>
+    </row>
+    <row r="113" spans="1:12">
+      <c r="A113" s="4"/>
+      <c r="B113" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="C113" s="5">
+        <v>0</v>
+      </c>
+      <c r="D113" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="8:10">
-      <c r="H9" t="s">
-        <v>34</v>
-      </c>
-      <c r="J9">
+      <c r="E113" s="5"/>
+      <c r="F113" s="5"/>
+      <c r="G113" s="5"/>
+      <c r="H113" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="I113" s="5"/>
+      <c r="J113" s="5">
+        <v>1</v>
+      </c>
+      <c r="K113" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="L113" s="6"/>
+    </row>
+    <row r="114" spans="1:12">
+      <c r="A114" s="4"/>
+      <c r="B114" s="5"/>
+      <c r="C114" s="5"/>
+      <c r="D114" s="5"/>
+      <c r="E114" s="5"/>
+      <c r="F114" s="5"/>
+      <c r="G114" s="5"/>
+      <c r="H114" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="I114" s="5"/>
+      <c r="J114" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="8:10">
-      <c r="H10" t="s">
-        <v>35</v>
-      </c>
-      <c r="J10">
+      <c r="K114" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="L114" s="6"/>
+    </row>
+    <row r="115" spans="1:12">
+      <c r="A115" s="4"/>
+      <c r="B115" s="5"/>
+      <c r="C115" s="5"/>
+      <c r="D115" s="5"/>
+      <c r="E115" s="5"/>
+      <c r="F115" s="5"/>
+      <c r="G115" s="5"/>
+      <c r="H115" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="I115" s="5"/>
+      <c r="J115" s="5">
+        <v>3</v>
+      </c>
+      <c r="K115" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="L115" s="6"/>
+    </row>
+    <row r="116" spans="1:12">
+      <c r="A116" s="4"/>
+      <c r="B116" s="5"/>
+      <c r="C116" s="5"/>
+      <c r="D116" s="5"/>
+      <c r="E116" s="5"/>
+      <c r="F116" s="5"/>
+      <c r="G116" s="5"/>
+      <c r="H116" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="I116" s="5"/>
+      <c r="J116" s="5">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="8:10">
-      <c r="H11" t="s">
-        <v>36</v>
-      </c>
-      <c r="J11">
+      <c r="K116" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="L116" s="6"/>
+    </row>
+    <row r="117" spans="1:12">
+      <c r="A117" s="4"/>
+      <c r="B117" s="5"/>
+      <c r="C117" s="5"/>
+      <c r="D117" s="5"/>
+      <c r="E117" s="5"/>
+      <c r="F117" s="5"/>
+      <c r="G117" s="5"/>
+      <c r="H117" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="I117" s="5"/>
+      <c r="J117" s="5">
+        <v>5</v>
+      </c>
+      <c r="K117" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="L117" s="6"/>
+    </row>
+    <row r="118" spans="1:12">
+      <c r="A118" s="4"/>
+      <c r="B118" s="5"/>
+      <c r="C118" s="5"/>
+      <c r="D118" s="5"/>
+      <c r="E118" s="5"/>
+      <c r="F118" s="5"/>
+      <c r="G118" s="5"/>
+      <c r="H118" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I118" s="5"/>
+      <c r="J118" s="5">
+        <v>6</v>
+      </c>
+      <c r="K118" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="L118" s="6"/>
+    </row>
+    <row r="119" spans="1:12">
+      <c r="A119" s="4"/>
+      <c r="B119" s="5"/>
+      <c r="C119" s="5"/>
+      <c r="D119" s="5"/>
+      <c r="E119" s="5"/>
+      <c r="F119" s="5"/>
+      <c r="G119" s="5"/>
+      <c r="H119" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="I119" s="5"/>
+      <c r="J119" s="5">
+        <v>7</v>
+      </c>
+      <c r="K119" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="L119" s="6"/>
+    </row>
+    <row r="120" spans="1:12">
+      <c r="A120" s="4"/>
+      <c r="B120" s="5"/>
+      <c r="C120" s="5"/>
+      <c r="D120" s="5"/>
+      <c r="E120" s="5"/>
+      <c r="F120" s="5"/>
+      <c r="G120" s="5"/>
+      <c r="H120" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="I120" s="5"/>
+      <c r="J120" s="5">
         <v>8</v>
       </c>
-    </row>
-    <row r="12" spans="8:11">
-      <c r="H12" t="s">
-        <v>37</v>
-      </c>
-      <c r="J12" t="s">
-        <v>38</v>
-      </c>
-      <c r="K12" t="s">
-        <v>39</v>
-      </c>
+      <c r="K120" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="L120" s="6"/>
+    </row>
+    <row r="121" spans="1:12">
+      <c r="A121" s="4"/>
+      <c r="B121" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C121" s="5">
+        <v>0</v>
+      </c>
+      <c r="D121" s="5">
+        <v>1</v>
+      </c>
+      <c r="E121" s="5"/>
+      <c r="F121" s="5"/>
+      <c r="G121" s="5"/>
+      <c r="H121" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="I121" s="5"/>
+      <c r="J121" s="5">
+        <v>1</v>
+      </c>
+      <c r="K121" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="L121" s="6"/>
+    </row>
+    <row r="122" spans="1:12">
+      <c r="A122" s="4"/>
+      <c r="B122" s="5"/>
+      <c r="C122" s="5"/>
+      <c r="D122" s="5"/>
+      <c r="E122" s="5"/>
+      <c r="F122" s="5"/>
+      <c r="G122" s="5"/>
+      <c r="H122" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="I122" s="5"/>
+      <c r="J122" s="5">
+        <v>2</v>
+      </c>
+      <c r="K122" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="L122" s="6"/>
+    </row>
+    <row r="123" spans="1:12">
+      <c r="A123" s="4"/>
+      <c r="B123" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C123" s="5">
+        <v>0</v>
+      </c>
+      <c r="D123" s="5">
+        <v>1</v>
+      </c>
+      <c r="E123" s="5"/>
+      <c r="F123" s="5"/>
+      <c r="G123" s="5"/>
+      <c r="H123" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="I123" s="5"/>
+      <c r="J123" s="5">
+        <v>1</v>
+      </c>
+      <c r="K123" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="L123" s="6"/>
+    </row>
+    <row r="124" spans="1:12">
+      <c r="A124" s="4"/>
+      <c r="B124" s="5"/>
+      <c r="C124" s="5"/>
+      <c r="D124" s="5"/>
+      <c r="E124" s="5"/>
+      <c r="F124" s="5"/>
+      <c r="G124" s="5"/>
+      <c r="H124" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="I124" s="5"/>
+      <c r="J124" s="5">
+        <v>2</v>
+      </c>
+      <c r="K124" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="L124" s="6"/>
+    </row>
+    <row r="125" spans="1:12">
+      <c r="A125" s="4"/>
+      <c r="B125" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="C125" s="5">
+        <v>0</v>
+      </c>
+      <c r="D125" s="5">
+        <v>1</v>
+      </c>
+      <c r="E125" s="5"/>
+      <c r="F125" s="5"/>
+      <c r="G125" s="5"/>
+      <c r="H125" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="I125" s="5"/>
+      <c r="J125" s="5">
+        <v>1</v>
+      </c>
+      <c r="K125" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="L125" s="6"/>
+    </row>
+    <row r="126" spans="1:12">
+      <c r="A126" s="4"/>
+      <c r="B126" s="5"/>
+      <c r="C126" s="5"/>
+      <c r="D126" s="5"/>
+      <c r="E126" s="5"/>
+      <c r="F126" s="5"/>
+      <c r="G126" s="5"/>
+      <c r="H126" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="I126" s="5"/>
+      <c r="J126" s="5">
+        <v>2</v>
+      </c>
+      <c r="K126" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="L126" s="6"/>
+    </row>
+    <row r="127" spans="1:12">
+      <c r="A127" s="4"/>
+      <c r="B127" s="5"/>
+      <c r="C127" s="5"/>
+      <c r="D127" s="5"/>
+      <c r="E127" s="5"/>
+      <c r="F127" s="5"/>
+      <c r="G127" s="5"/>
+      <c r="H127" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="I127" s="5"/>
+      <c r="J127" s="5">
+        <v>3</v>
+      </c>
+      <c r="K127" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="L127" s="6"/>
+    </row>
+    <row r="128" spans="1:12">
+      <c r="A128" s="4"/>
+      <c r="B128" s="5"/>
+      <c r="C128" s="5"/>
+      <c r="D128" s="5"/>
+      <c r="E128" s="5"/>
+      <c r="F128" s="5"/>
+      <c r="G128" s="5"/>
+      <c r="H128" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="I128" s="5"/>
+      <c r="J128" s="5">
+        <v>4</v>
+      </c>
+      <c r="K128" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="L128" s="6"/>
+    </row>
+    <row r="129" spans="1:12">
+      <c r="A129" s="4"/>
+      <c r="B129" s="5"/>
+      <c r="C129" s="5"/>
+      <c r="D129" s="5"/>
+      <c r="E129" s="5"/>
+      <c r="F129" s="5"/>
+      <c r="G129" s="5"/>
+      <c r="H129" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="I129" s="5"/>
+      <c r="J129" s="5">
+        <v>5</v>
+      </c>
+      <c r="K129" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="L129" s="6"/>
+    </row>
+    <row r="130" spans="1:12">
+      <c r="A130" s="4"/>
+      <c r="B130" s="5"/>
+      <c r="C130" s="5"/>
+      <c r="D130" s="5"/>
+      <c r="E130" s="5"/>
+      <c r="F130" s="5"/>
+      <c r="G130" s="5"/>
+      <c r="H130" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="I130" s="5"/>
+      <c r="J130" s="5">
+        <v>6</v>
+      </c>
+      <c r="K130" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="L130" s="6"/>
+    </row>
+    <row r="131" spans="1:12">
+      <c r="A131" s="4"/>
+      <c r="B131" s="5"/>
+      <c r="C131" s="5"/>
+      <c r="D131" s="5"/>
+      <c r="E131" s="5"/>
+      <c r="F131" s="5"/>
+      <c r="G131" s="5"/>
+      <c r="H131" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="I131" s="5"/>
+      <c r="J131" s="5">
+        <v>7</v>
+      </c>
+      <c r="K131" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="L131" s="6"/>
+    </row>
+    <row r="132" spans="1:12">
+      <c r="A132" s="4"/>
+      <c r="B132" s="5"/>
+      <c r="C132" s="5"/>
+      <c r="D132" s="5"/>
+      <c r="E132" s="5"/>
+      <c r="F132" s="5"/>
+      <c r="G132" s="5"/>
+      <c r="H132" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="I132" s="5"/>
+      <c r="J132" s="5">
+        <v>8</v>
+      </c>
+      <c r="K132" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="L132" s="6"/>
+    </row>
+    <row r="133" spans="1:12">
+      <c r="A133" s="4"/>
+      <c r="B133" s="5"/>
+      <c r="C133" s="5"/>
+      <c r="D133" s="5"/>
+      <c r="E133" s="5"/>
+      <c r="F133" s="5"/>
+      <c r="G133" s="5"/>
+      <c r="H133" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="I133" s="5"/>
+      <c r="J133" s="5">
+        <v>9</v>
+      </c>
+      <c r="K133" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="L133" s="6"/>
+    </row>
+    <row r="134" spans="1:12">
+      <c r="A134" s="4"/>
+      <c r="B134" s="5"/>
+      <c r="C134" s="5"/>
+      <c r="D134" s="5"/>
+      <c r="E134" s="5"/>
+      <c r="F134" s="5"/>
+      <c r="G134" s="5"/>
+      <c r="H134" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="I134" s="5"/>
+      <c r="J134" s="5">
+        <v>10</v>
+      </c>
+      <c r="K134" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="L134" s="6"/>
+    </row>
+    <row r="135" spans="1:12">
+      <c r="A135" s="4"/>
+      <c r="B135" s="5"/>
+      <c r="C135" s="5"/>
+      <c r="D135" s="5"/>
+      <c r="E135" s="5"/>
+      <c r="F135" s="5"/>
+      <c r="G135" s="5"/>
+      <c r="H135" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="I135" s="5"/>
+      <c r="J135" s="5">
+        <v>11</v>
+      </c>
+      <c r="K135" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="L135" s="6"/>
+    </row>
+    <row r="136" spans="1:12">
+      <c r="A136" s="4"/>
+      <c r="B136" s="5"/>
+      <c r="C136" s="5"/>
+      <c r="D136" s="5"/>
+      <c r="E136" s="5"/>
+      <c r="F136" s="5"/>
+      <c r="G136" s="5"/>
+      <c r="H136" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="I136" s="5"/>
+      <c r="J136" s="5">
+        <v>12</v>
+      </c>
+      <c r="K136" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="L136" s="6"/>
+    </row>
+    <row r="137" spans="1:12">
+      <c r="A137" s="4"/>
+      <c r="B137" s="5"/>
+      <c r="C137" s="5"/>
+      <c r="D137" s="5"/>
+      <c r="E137" s="5"/>
+      <c r="F137" s="5"/>
+      <c r="G137" s="5"/>
+      <c r="H137" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="I137" s="5"/>
+      <c r="J137" s="5">
+        <v>13</v>
+      </c>
+      <c r="K137" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="L137" s="6"/>
+    </row>
+    <row r="138" spans="1:12">
+      <c r="A138" s="4"/>
+      <c r="B138" s="5"/>
+      <c r="C138" s="5"/>
+      <c r="D138" s="5"/>
+      <c r="E138" s="5"/>
+      <c r="F138" s="5"/>
+      <c r="G138" s="5"/>
+      <c r="H138" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="I138" s="5"/>
+      <c r="J138" s="5">
+        <v>14</v>
+      </c>
+      <c r="K138" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="L138" s="6"/>
+    </row>
+    <row r="139" spans="1:12">
+      <c r="A139" s="4"/>
+      <c r="B139" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="C139" s="5">
+        <v>0</v>
+      </c>
+      <c r="D139" s="5">
+        <v>1</v>
+      </c>
+      <c r="E139" s="5"/>
+      <c r="F139" s="5"/>
+      <c r="G139" s="5"/>
+      <c r="H139" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="I139" s="5"/>
+      <c r="J139" s="5">
+        <v>1</v>
+      </c>
+      <c r="K139" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="L139" s="6"/>
+    </row>
+    <row r="140" spans="1:12">
+      <c r="A140" s="7"/>
+      <c r="B140" s="8"/>
+      <c r="C140" s="8"/>
+      <c r="D140" s="8"/>
+      <c r="E140" s="8"/>
+      <c r="F140" s="8"/>
+      <c r="G140" s="8"/>
+      <c r="H140" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="I140" s="8"/>
+      <c r="J140" s="8">
+        <v>2</v>
+      </c>
+      <c r="K140" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="L140" s="9"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="155">
     <mergeCell ref="H1:L1"/>
+    <mergeCell ref="A4:A8"/>
+    <mergeCell ref="A9:A17"/>
+    <mergeCell ref="A18:A31"/>
+    <mergeCell ref="A32:A47"/>
+    <mergeCell ref="A48:A51"/>
+    <mergeCell ref="A52:A54"/>
+    <mergeCell ref="A55:A58"/>
+    <mergeCell ref="A59:A62"/>
+    <mergeCell ref="A63:A69"/>
+    <mergeCell ref="A70:A75"/>
+    <mergeCell ref="A76:A78"/>
+    <mergeCell ref="A79:A82"/>
+    <mergeCell ref="A83:A93"/>
+    <mergeCell ref="A94:A99"/>
+    <mergeCell ref="A100:A102"/>
+    <mergeCell ref="A103:A109"/>
+    <mergeCell ref="A110:A112"/>
+    <mergeCell ref="A113:A120"/>
+    <mergeCell ref="A121:A122"/>
+    <mergeCell ref="A123:A124"/>
+    <mergeCell ref="A125:A138"/>
+    <mergeCell ref="A139:A140"/>
+    <mergeCell ref="B4:B8"/>
+    <mergeCell ref="B9:B17"/>
+    <mergeCell ref="B18:B31"/>
+    <mergeCell ref="B32:B47"/>
+    <mergeCell ref="B48:B51"/>
+    <mergeCell ref="B52:B54"/>
+    <mergeCell ref="B55:B58"/>
+    <mergeCell ref="B59:B62"/>
+    <mergeCell ref="B63:B69"/>
+    <mergeCell ref="B70:B75"/>
+    <mergeCell ref="B76:B78"/>
+    <mergeCell ref="B79:B82"/>
+    <mergeCell ref="B83:B93"/>
+    <mergeCell ref="B94:B99"/>
+    <mergeCell ref="B100:B102"/>
+    <mergeCell ref="B103:B109"/>
+    <mergeCell ref="B110:B112"/>
+    <mergeCell ref="B113:B120"/>
+    <mergeCell ref="B121:B122"/>
+    <mergeCell ref="B123:B124"/>
+    <mergeCell ref="B125:B138"/>
+    <mergeCell ref="B139:B140"/>
+    <mergeCell ref="C4:C8"/>
+    <mergeCell ref="C9:C17"/>
+    <mergeCell ref="C18:C31"/>
+    <mergeCell ref="C32:C47"/>
+    <mergeCell ref="C48:C51"/>
+    <mergeCell ref="C52:C54"/>
+    <mergeCell ref="C55:C58"/>
+    <mergeCell ref="C59:C62"/>
+    <mergeCell ref="C63:C69"/>
+    <mergeCell ref="C70:C75"/>
+    <mergeCell ref="C76:C78"/>
+    <mergeCell ref="C79:C82"/>
+    <mergeCell ref="C83:C93"/>
+    <mergeCell ref="C94:C99"/>
+    <mergeCell ref="C100:C102"/>
+    <mergeCell ref="C103:C109"/>
+    <mergeCell ref="C110:C112"/>
+    <mergeCell ref="C113:C120"/>
+    <mergeCell ref="C121:C122"/>
+    <mergeCell ref="C123:C124"/>
+    <mergeCell ref="C125:C138"/>
+    <mergeCell ref="C139:C140"/>
+    <mergeCell ref="D4:D8"/>
+    <mergeCell ref="D9:D17"/>
+    <mergeCell ref="D18:D31"/>
+    <mergeCell ref="D32:D47"/>
+    <mergeCell ref="D48:D51"/>
+    <mergeCell ref="D52:D54"/>
+    <mergeCell ref="D55:D58"/>
+    <mergeCell ref="D59:D62"/>
+    <mergeCell ref="D63:D69"/>
+    <mergeCell ref="D70:D75"/>
+    <mergeCell ref="D76:D78"/>
+    <mergeCell ref="D79:D82"/>
+    <mergeCell ref="D83:D93"/>
+    <mergeCell ref="D94:D99"/>
+    <mergeCell ref="D100:D102"/>
+    <mergeCell ref="D103:D109"/>
+    <mergeCell ref="D110:D112"/>
+    <mergeCell ref="D113:D120"/>
+    <mergeCell ref="D121:D122"/>
+    <mergeCell ref="D123:D124"/>
+    <mergeCell ref="D125:D138"/>
+    <mergeCell ref="D139:D140"/>
+    <mergeCell ref="E4:E8"/>
+    <mergeCell ref="E9:E17"/>
+    <mergeCell ref="E18:E31"/>
+    <mergeCell ref="E32:E47"/>
+    <mergeCell ref="E48:E51"/>
+    <mergeCell ref="E52:E54"/>
+    <mergeCell ref="E55:E58"/>
+    <mergeCell ref="E59:E62"/>
+    <mergeCell ref="E63:E69"/>
+    <mergeCell ref="E70:E75"/>
+    <mergeCell ref="E76:E78"/>
+    <mergeCell ref="E79:E82"/>
+    <mergeCell ref="E83:E93"/>
+    <mergeCell ref="E94:E99"/>
+    <mergeCell ref="E100:E102"/>
+    <mergeCell ref="E103:E109"/>
+    <mergeCell ref="E110:E112"/>
+    <mergeCell ref="E113:E120"/>
+    <mergeCell ref="E121:E122"/>
+    <mergeCell ref="E123:E124"/>
+    <mergeCell ref="E125:E138"/>
+    <mergeCell ref="E139:E140"/>
+    <mergeCell ref="F4:F8"/>
+    <mergeCell ref="F9:F17"/>
+    <mergeCell ref="F18:F31"/>
+    <mergeCell ref="F32:F47"/>
+    <mergeCell ref="F48:F51"/>
+    <mergeCell ref="F52:F54"/>
+    <mergeCell ref="F55:F58"/>
+    <mergeCell ref="F59:F62"/>
+    <mergeCell ref="F63:F69"/>
+    <mergeCell ref="F70:F75"/>
+    <mergeCell ref="F76:F78"/>
+    <mergeCell ref="F79:F82"/>
+    <mergeCell ref="F83:F93"/>
+    <mergeCell ref="F94:F99"/>
+    <mergeCell ref="F100:F102"/>
+    <mergeCell ref="F103:F109"/>
+    <mergeCell ref="F110:F112"/>
+    <mergeCell ref="F113:F120"/>
+    <mergeCell ref="F121:F122"/>
+    <mergeCell ref="F123:F124"/>
+    <mergeCell ref="F125:F138"/>
+    <mergeCell ref="F139:F140"/>
+    <mergeCell ref="G4:G8"/>
+    <mergeCell ref="G9:G17"/>
+    <mergeCell ref="G18:G31"/>
+    <mergeCell ref="G32:G47"/>
+    <mergeCell ref="G48:G51"/>
+    <mergeCell ref="G52:G54"/>
+    <mergeCell ref="G55:G58"/>
+    <mergeCell ref="G59:G62"/>
+    <mergeCell ref="G63:G69"/>
+    <mergeCell ref="G70:G75"/>
+    <mergeCell ref="G76:G78"/>
+    <mergeCell ref="G79:G82"/>
+    <mergeCell ref="G83:G93"/>
+    <mergeCell ref="G94:G99"/>
+    <mergeCell ref="G100:G102"/>
+    <mergeCell ref="G103:G109"/>
+    <mergeCell ref="G110:G112"/>
+    <mergeCell ref="G113:G120"/>
+    <mergeCell ref="G121:G122"/>
+    <mergeCell ref="G123:G124"/>
+    <mergeCell ref="G125:G138"/>
+    <mergeCell ref="G139:G140"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>